--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,117 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122246488</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100388</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Coptidium lapponicum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Tzvelev</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Runån, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>580865</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7010672</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Y-Sol-0385</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>122246488</v>
       </c>
       <c r="B4" t="n">
-        <v>100388</v>
+        <v>100396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>122246488</v>
       </c>
       <c r="B4" t="n">
-        <v>100396</v>
+        <v>100398</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>122246488</v>
       </c>
       <c r="B4" t="n">
-        <v>100414</v>
+        <v>100424</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>122246488</v>
       </c>
       <c r="B4" t="n">
-        <v>100424</v>
+        <v>100436</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>122246488</v>
       </c>
       <c r="B4" t="n">
-        <v>100436</v>
+        <v>100441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>122246488</v>
       </c>
       <c r="B4" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,11 +916,6 @@
       </c>
       <c r="E4" t="n">
         <v>1365</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lappranunkel</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>122246488</v>
       </c>
       <c r="B4" t="n">
-        <v>100450</v>
+        <v>100463</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,6 +916,11 @@
       </c>
       <c r="E4" t="n">
         <v>1365</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lappranunkel</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>122246488</v>
       </c>
       <c r="B4" t="n">
-        <v>100463</v>
+        <v>100476</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>122246488</v>
       </c>
       <c r="B4" t="n">
-        <v>100476</v>
+        <v>100479</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>122246488</v>
       </c>
       <c r="B4" t="n">
-        <v>100479</v>
+        <v>100480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>122246488</v>
       </c>
       <c r="B4" t="n">
-        <v>100480</v>
+        <v>100483</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>122246488</v>
       </c>
       <c r="B4" t="n">
-        <v>100586</v>
+        <v>100594</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 8669-2023 artfynd.xlsx
+++ b/artfynd/A 8669-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,117 +897,6 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>122246488</v>
-      </c>
-      <c r="B4" t="n">
-        <v>100594</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>1365</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lappranunkel</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Coptidium lapponicum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) Tzvelev</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Runån, Ång</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>580865</v>
-      </c>
-      <c r="R4" t="n">
-        <v>7010672</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Helgum</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Y-Sol-0385</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2023-07-16</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Anders Malmsten</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
